--- a/banks/TANDEM FINANCIALS.xlsx
+++ b/banks/TANDEM FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tandem Bank Limited — Cash Flow Summary by Year</a:t>
+              <a:t>Tandem Bank Limited — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -307,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -350,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +395,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Tandem Bank Limited — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Tandem Bank Limited — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Tandem Bank Limited — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -593,30 +1168,30 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q11</f>
+              <f>'Overview'!AO11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$AP$11:$AT$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -648,8 +1223,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -688,12 +1263,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -703,9 +1278,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -715,19 +1290,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1689,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,14 +1725,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£'000)</t>
+          <t>Balance Sheet Summary (£'000)</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1792,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1156,234 +1821,294 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) operating activities</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2489828</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3155197</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3859400</v>
+      </c>
       <c r="E6" s="5" t="n">
-        <v>309350</v>
+        <v>1926197</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>201526</v>
+        <v>853719</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>201526</v>
+        <v>853719</v>
       </c>
       <c r="K6" t="n">
-        <v>309350</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>1926197</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3859400</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3155197</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2489828</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>14.2</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>15.2</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>16.1</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>17.4</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>15.53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1284901</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1219256</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1280896</v>
+      </c>
       <c r="E7" s="5" t="n">
-        <v>-61572</v>
+        <v>1078369</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-2075</v>
+        <v>436845</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-2075</v>
+        <v>436845</v>
       </c>
       <c r="K7" t="n">
-        <v>-61572</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>1078369</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1280896</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1219256</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1284901</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>14.2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>15.2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>16.1</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>17.4</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>15.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) financing activities</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+          <t>Customer accounts</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2260738</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2916365</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3639407</v>
+      </c>
       <c r="E8" s="5" t="n">
-        <v>76464</v>
+        <v>1754868</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>12309</v>
+        <v>771161</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) financing activities</t>
+          <t>Customer accounts</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12309</v>
+        <v>771161</v>
       </c>
       <c r="K8" t="n">
-        <v>76464</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>1754868</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3639407</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2916365</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2260738</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>14.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>15.2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>18.8</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>20.21</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>18.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>187930</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>177679</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>156571</v>
+      </c>
       <c r="E9" s="5" t="n">
-        <v>700930</v>
+        <v>115178</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>376688</v>
+        <v>41620</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>376688</v>
+        <v>41620</v>
       </c>
       <c r="K9" t="n">
-        <v>700930</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>115178</v>
+      </c>
+      <c r="L9" t="n">
+        <v>156571</v>
+      </c>
+      <c r="M9" t="n">
+        <v>177679</v>
+      </c>
+      <c r="N9" t="n">
+        <v>187930</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>4.6</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>10.02</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>9.039999999999999</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="AP10" t="n">
         <v>331</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>314.1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>636</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>534.75</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AT10" t="n">
         <v>443.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Profit &amp; Loss Summary (£'000)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="AQ11" t="n">
         <v>155.5</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AR11" t="n">
         <v>270.6</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AS11" t="n">
         <v>263.1</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AT11" t="n">
         <v>194.3</v>
       </c>
     </row>
@@ -1418,197 +2143,791 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>86097</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>80410</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>75912</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>57227</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>14802</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>14802</v>
+      </c>
+      <c r="S13" t="n">
+        <v>57227</v>
+      </c>
+      <c r="T13" t="n">
+        <v>75912</v>
+      </c>
+      <c r="U13" t="n">
+        <v>80410</v>
+      </c>
+      <c r="V13" t="n">
+        <v>86097</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Administrative expenses (Operating Expenses)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-64142</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-62957</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-62045</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-52218</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-30508</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Administrative expenses (Operating Expenses)</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-30508</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-52218</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-62045</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-62957</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-64142</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) for the Year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3458</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11512</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-1654</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-17853</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) for the Year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>-17853</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1654</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3600</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11512</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3458</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>177679</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>156571</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>115535</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>41620</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>47018</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>47018</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>41620</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>115535</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>156571</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>177679</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3805</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>12034</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>4240</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-1728</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-17707</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>-17707</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-1728</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>4240</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>12034</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>9074</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>36796</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>75286</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>12309</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>12309</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>75286</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>36796</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9074</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>6446</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>187930</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>177679</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>156571</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>115178</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>41620</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>41620</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>115178</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>156571</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>177679</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>187930</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n">
+        <v>309350</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>201526</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>201526</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>309350</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n">
+        <v>-61572</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-2075</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>-2075</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-61572</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n">
+        <v>76464</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>12309</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>12309</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>76464</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n">
+        <v>700930</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>376688</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>376688</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>700930</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>15.53%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>17.40%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>16.1%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>14.2%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>15.53%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>17.40%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>16.1%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>14.2%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>18.11%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>20.21%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>18.8%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>14.2%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>9.04%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>10.02%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>9.8%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>8.8%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>4.6%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>443.40%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>534.75%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>636.0%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>314.1%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>331%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>194.30%</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>263.10%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>270.6%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>155.5%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n"/>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="F38" s="6" t="n"/>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Cash flow is blank for FY2023-FY2025 (FRS 102 qualifying-entity exemption took effect from FY2023 - see Cash Flow Statement sheet note) and ratios are on a wider TML Group basis, not Tandem Bank Limited solo (see each Pillar 3 sheet's source note) - two different, independently-documented basis differences within this single workbook.</t>
         </is>
@@ -1616,7 +2935,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1624,6 +2943,570 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group basis, % of RWEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.53%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.40%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>196155</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>192343</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>175438</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>119883</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>39742</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group basis, % of RWEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>18.11%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.21%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted assets (RWEA)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1083333</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>951607</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>931650</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>790158</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>280843</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>RWA Breakdown</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: TML's Pillar 3 Disclosures do not include a UK OV1-style RWA breakdown-by-risk-category table in any year FY2021-FY2025 (all 4 available editions checked directly - each is a short document, 9-15 pages, consistent with the Group's stated 'small, non-complex' institution status under UK CRR Article 4(145) and the reduced Pillar 3 disclosure regime of Article 433(b), the same basis already noted for MREL Ratio's non-disclosure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1769,7 +3652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1933,7 +3816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2097,7 +3980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2223,6 +4106,1880 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank (Company-only) basis, £'000. FY2022 shown as originally reported - see source note at bottom (restatement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances at central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>584887</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1497095</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2421938</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>679659</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>360378</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>35121</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>33267</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>34287</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>21271</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>16310</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1284901</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1219256</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1280896</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1078369</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>436845</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Debt securities</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>554658</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>370151</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>56609</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>91210</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>30215</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>6383</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>11304</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>24353</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>29592</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Equity shares</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>3667</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>3533</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>2758</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2309</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>11395</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>10296</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>27830</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>23287</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>5639</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Prepayments and accrued income</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n">
+        <v>493</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax asset</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>8816</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>10295</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>10236</v>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2489828</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>3155197</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3859400</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1926197</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>853719</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Deposits by banks / Borrowings from banks</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>10113</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>23798</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>30934</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>43527</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>40013</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Customer accounts</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>2260738</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>2916365</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3639407</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1754868</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>771161</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>4988</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2503</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>11197</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>7057</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>6467</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>15529</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1613</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>5162</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Accruals and deferred income</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n">
+        <v>735</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>405</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Subordinated liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>19592</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>19323</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>18943</v>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2301898</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2977518</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3702829</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1811019</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>812099</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Called-up share capital</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>200999</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>192999</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>187999</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>152339</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>75875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>85444</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>86998</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>82924</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>80051</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>80051</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Retained reserves (Available for sale reserve + Retained earnings/(losses))</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>-98513</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-102318</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-114352</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-117212</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-114306</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>187930</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>177679</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>156571</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>115178</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>41620</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Total Liabilities and Equity</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2489828</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>3155197</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3859400</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1926197</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>853719</v>
+      </c>
+    </row>
+    <row r="30" ht="280" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Tandem Bank Limited's own (Company-only, not TML Group) figures, £'000:
+FY2025: Annual Report and Accounts for the year ended 31 December 2025, p.25 (2025)/26 (2024 comparative) (Statement of Financial Position), p.24 (2025)/25 (2024 comparative) (Income Statement and Statement of Other Comprehensive Income), p.26 (2025)/27 (2024 comparative) (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2024: as reported in the FY2025 Annual Report's own comparative column (no separate FY2024 filing covers this line item set at this granularity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2023: Annual Report and Accounts for the year ended 31 December 2023, p.33 (Statement of Financial Position), p.32 (Income Statement and Statement of Other Comprehensive Income), p.34 (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2022: Annual Report and Accounts for the year ended 31 December 2022, p.43 (Statement of Financial Position), p.42 (Income Statement and Statement of Other Comprehensive Income), p.44 (Statement of Changes in Equity) - as originally reported, NOT the FY2023 Annual Report's later restated comparative - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2021: Annual Report and Accounts for the year ended 31 December 2021, p.46 (Income Statement and Statement of Other Comprehensive Income), p.47 (Statement of Financial Position), p.48 (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+ENTITY NOTE: 'Tandem Bank Limited' (company number 00955491, FRN 204479) is the PRA-authorised entity built here. It is NOT the same company as 'Tandem Money Limited' (company number 08628614) - a related, similarly-named entity that briefly used the name 'Tandem Bank Limited' itself from Dec 2015-May 2017 before becoming Tandem Money Limited (TML), the non-bank holding company that today sits above Tandem Bank Limited (TBL) in the group structure. Company 00955491 was previously 'Harrods Bank Limited' (renamed 12 Jan 2018) - Tandem acquired Harrods Bank's banking licence in 2017 to become a PRA-authorised deposit-taker quickly; it traces further back to 'Harrods Trust Limited' and, before that, 'Harrods (Knightsbridge) Limited' (incorporated 1969), which is why Companies House shows an incorporation date decades before Tandem's own 2013 founding. Confirmed via Companies House (previous-names history) and cross-checked against the FRN in Banks List 2608.xlsx.
+RESTATEMENT NOTE: FY2022's Balance Sheet, Profit &amp; Loss and Statement of Changes in Equity figures shown here are Tandem Bank Limited's own AS-ORIGINALLY-PUBLISHED figures (from the FY2022 Annual Report and Accounts), not the later FY2023 Annual Report's restated FY2022 comparative column (which reclassified certain effective interest rate balances and reflected motor finance hire purchase receivables as secured rather than unsecured lending - Note 2 of the FY2023 Annual Report). This creates a genuine, documented, non-plugged break at the FY2022/FY2023 boundary on the Statement of Changes in Equity sheet: FY2022's own closing Total equity (£115,178k) does not equal the FY2023 Annual Report's restated FY2023 opening balance (£115,535k, a £357k difference, itself split into a +£1,737k Other Reserves capital-contribution reclassification and a -£1,380k Retained earnings adjustment) - both figures are shown, connected by an explicit 'Restatement (per Note 2 of the FY2023 Annual Report)' row rather than silently smoothed over. The same restatement affects Loans and advances to customers on the Balance Sheet (FY2022 shown here as £1,078,369k as originally reported vs. £1,080,282k in the FY2023 Annual Report's restated comparative) and the FY2022 Profit &amp; Loss (originally reported: Interest income £74,932k, Loss on operating activities before tax £(6,933)k, Loss for the year £(1,654)k; FY2023 Annual Report's restated comparative: Interest income £72,374k, Loss before tax £(9,491)k, Loss for the year £(4,212)k).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A30:F30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Income Statement and Statement of Other Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank (Company-only) basis, £'000. FY2022 shown as originally reported - see source note at bottom (restatement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>200193</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>239980</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>203197</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>74932</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>21588</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-112547</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-161034</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-125307</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-19522</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-6453</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net Interest Income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>87646</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>78946</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>77890</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>55410</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>15135</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commissions income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commissions expense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-164</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-98</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-103</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-163</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-482</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Net (loss)/gain in derivatives and hedge ineffectiveness</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>-1426</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1542</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>-1890</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1954</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>86097</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>80410</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>75912</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>57227</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>14802</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Administrative expenses (Operating Expenses)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>-64142</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-62957</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-62045</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-52218</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-30508</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Provision for bad and doubtful debts</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-25410</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-17053</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-19415</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-13412</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-1705</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Gain/(loss) on sale of financial assets/loan portfolios</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>8930</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>11220</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2752</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-569</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Impairment of intercompany balances</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) on Operating Activities before Tax</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>5475</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>11620</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2796</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6933</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-18030</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Tax charge/credit on profit/(loss)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-2017</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-108</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>6396</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>5279</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(Loss) for the Year</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3458</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>11512</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-1654</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-17853</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income/(Expense)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Available for sale investments - fair value gain/(loss) on debt securities</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>246</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>-59</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>303</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-328</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Available for sale investments - fair value gain on equity shares</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>775</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>339</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Deferred income tax on items of other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-33</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-194</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-113</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-85</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-177</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income/(Expense) for the Year, net of tax</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>347</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>522</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-74</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total Comprehensive Profit/(Loss) for the Year</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>3805</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>12034</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>4240</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-1728</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-17707</v>
+      </c>
+    </row>
+    <row r="27" ht="300" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Tandem Bank Limited's own (Company-only, not TML Group) figures, £'000:
+FY2025: Annual Report and Accounts for the year ended 31 December 2025, p.25 (2025)/26 (2024 comparative) (Statement of Financial Position), p.24 (2025)/25 (2024 comparative) (Income Statement and Statement of Other Comprehensive Income), p.26 (2025)/27 (2024 comparative) (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2024: as reported in the FY2025 Annual Report's own comparative column (no separate FY2024 filing covers this line item set at this granularity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2023: Annual Report and Accounts for the year ended 31 December 2023, p.33 (Statement of Financial Position), p.32 (Income Statement and Statement of Other Comprehensive Income), p.34 (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2022: Annual Report and Accounts for the year ended 31 December 2022, p.43 (Statement of Financial Position), p.42 (Income Statement and Statement of Other Comprehensive Income), p.44 (Statement of Changes in Equity) - as originally reported, NOT the FY2023 Annual Report's later restated comparative - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2021: Annual Report and Accounts for the year ended 31 December 2021, p.46 (Income Statement and Statement of Other Comprehensive Income), p.47 (Statement of Financial Position), p.48 (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+ENTITY NOTE: 'Tandem Bank Limited' (company number 00955491, FRN 204479) is the PRA-authorised entity built here. It is NOT the same company as 'Tandem Money Limited' (company number 08628614) - a related, similarly-named entity that briefly used the name 'Tandem Bank Limited' itself from Dec 2015-May 2017 before becoming Tandem Money Limited (TML), the non-bank holding company that today sits above Tandem Bank Limited (TBL) in the group structure. Company 00955491 was previously 'Harrods Bank Limited' (renamed 12 Jan 2018) - Tandem acquired Harrods Bank's banking licence in 2017 to become a PRA-authorised deposit-taker quickly; it traces further back to 'Harrods Trust Limited' and, before that, 'Harrods (Knightsbridge) Limited' (incorporated 1969), which is why Companies House shows an incorporation date decades before Tandem's own 2013 founding. Confirmed via Companies House (previous-names history) and cross-checked against the FRN in Banks List 2608.xlsx.
+RESTATEMENT NOTE: FY2022's Balance Sheet, Profit &amp; Loss and Statement of Changes in Equity figures shown here are Tandem Bank Limited's own AS-ORIGINALLY-PUBLISHED figures (from the FY2022 Annual Report and Accounts), not the later FY2023 Annual Report's restated FY2022 comparative column (which reclassified certain effective interest rate balances and reflected motor finance hire purchase receivables as secured rather than unsecured lending - Note 2 of the FY2023 Annual Report). This creates a genuine, documented, non-plugged break at the FY2022/FY2023 boundary on the Statement of Changes in Equity sheet: FY2022's own closing Total equity (£115,178k) does not equal the FY2023 Annual Report's restated FY2023 opening balance (£115,535k, a £357k difference, itself split into a +£1,737k Other Reserves capital-contribution reclassification and a -£1,380k Retained earnings adjustment) - both figures are shown, connected by an explicit 'Restatement (per Note 2 of the FY2023 Annual Report)' row rather than silently smoothed over. The same restatement affects Loans and advances to customers on the Balance Sheet (FY2022 shown here as £1,078,369k as originally reported vs. £1,080,282k in the FY2023 Annual Report's restated comparative) and the FY2022 Profit &amp; Loss (originally reported: Interest income £74,932k, Loss on operating activities before tax £(6,933)k, Loss for the year £(1,654)k; FY2023 Annual Report's restated comparative: Interest income £72,374k, Loss before tax £(9,491)k, Loss for the year £(4,212)k).
+FY2022's Income Statement in its own Annual Report split figures into Continuing/Discontinued Operations columns (the Bank sold a loan portfolio and disposed of a business line that year); the '2022 Total' column shown here sums both. FY2021's Fees and commissions income (£11k) is a Discontinued Operations item; FY2022 had none in either column, shown as 0 rather than blank since the line is genuinely nil that year, not undisclosed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank (Company-only) basis, £'000. Chronological, oldest to newest. See source note at bottom (FY2022/FY2023 restatement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Called-up Share Capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Available for Sale Reserve</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Other Reserves</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings/(losses)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>63566</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1207</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>80051</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-97806</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>47018</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n">
+        <v>-17853</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-17853</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Gain relating to available for sale investments</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>323</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax on items of other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>-177</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n">
+        <v>-177</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n">
+        <v>-17853</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-17707</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Shares issued, net of expenses</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>12309</v>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n">
+        <v>12309</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>75875</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1353</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>80051</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-115659</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>41620</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n">
+        <v>-1654</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-1654</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Gain relating to available for sale investments</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax on items of other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>-85</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n">
+        <v>-74</v>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n">
+        <v>-1654</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1728</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Shares issued, net of expenses</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>76464</v>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n">
+        <v>76464</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Capital contribution</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>-1178</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-1178</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2022 (as originally reported)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>152339</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1279</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>80051</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-118491</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>115178</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Restatement (per Note 2 of the FY2023 Annual Report - reclassification of effective interest rate balances and motor finance hire purchase receivables)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n">
+        <v>1737</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-1380</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2023 (restated)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>152339</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1279</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>81788</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-119871</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>115535</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Gain relating to available for sale investments</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>753</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax on items of other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n">
+        <v>-113</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n">
+        <v>-113</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive profit for the year</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>4240</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Shares issued, net of expenses</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>35660</v>
+      </c>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n">
+        <v>35660</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Capital contribution</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n">
+        <v>1136</v>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>187999</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1919</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>82924</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-116271</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>156571</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n">
+        <v>11512</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>11512</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Gain relating to available for sale investments</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n">
+        <v>716</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax on items of other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n">
+        <v>-194</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n">
+        <v>-194</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive profit for the year</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n">
+        <v>522</v>
+      </c>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n">
+        <v>11512</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>12034</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Fair value adjustment of loans and advances to customers - on acquisition date</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n">
+        <v>4287</v>
+      </c>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n">
+        <v>4287</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Fair value adjustment of loans and advances to customers - amortisation</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n">
+        <v>-213</v>
+      </c>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n">
+        <v>-213</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Shares issued, net of expenses</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>192999</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>2441</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>86998</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>-104759</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>177679</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n">
+        <v>3458</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>3458</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Gain relating to available for sale investments</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n">
+        <v>380</v>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax on items of other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n">
+        <v>-33</v>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive profit for the year</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n">
+        <v>347</v>
+      </c>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n">
+        <v>3458</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Fair value adjustment of loans and advances to customers - amortisation</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n">
+        <v>-1554</v>
+      </c>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n">
+        <v>-1554</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Shares issued, net of expenses</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>200999</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>2788</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>85444</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>-101301</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>187930</v>
+      </c>
+    </row>
+    <row r="43" ht="300" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Tandem Bank Limited's own (Company-only, not TML Group) figures, £'000:
+FY2025: Annual Report and Accounts for the year ended 31 December 2025, p.25 (2025)/26 (2024 comparative) (Statement of Financial Position), p.24 (2025)/25 (2024 comparative) (Income Statement and Statement of Other Comprehensive Income), p.26 (2025)/27 (2024 comparative) (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2024: as reported in the FY2025 Annual Report's own comparative column (no separate FY2024 filing covers this line item set at this granularity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2023: Annual Report and Accounts for the year ended 31 December 2023, p.33 (Statement of Financial Position), p.32 (Income Statement and Statement of Other Comprehensive Income), p.34 (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2022: Annual Report and Accounts for the year ended 31 December 2022, p.43 (Statement of Financial Position), p.42 (Income Statement and Statement of Other Comprehensive Income), p.44 (Statement of Changes in Equity) - as originally reported, NOT the FY2023 Annual Report's later restated comparative - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2021: Annual Report and Accounts for the year ended 31 December 2021, p.46 (Income Statement and Statement of Other Comprehensive Income), p.47 (Statement of Financial Position), p.48 (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+ENTITY NOTE: 'Tandem Bank Limited' (company number 00955491, FRN 204479) is the PRA-authorised entity built here. It is NOT the same company as 'Tandem Money Limited' (company number 08628614) - a related, similarly-named entity that briefly used the name 'Tandem Bank Limited' itself from Dec 2015-May 2017 before becoming Tandem Money Limited (TML), the non-bank holding company that today sits above Tandem Bank Limited (TBL) in the group structure. Company 00955491 was previously 'Harrods Bank Limited' (renamed 12 Jan 2018) - Tandem acquired Harrods Bank's banking licence in 2017 to become a PRA-authorised deposit-taker quickly; it traces further back to 'Harrods Trust Limited' and, before that, 'Harrods (Knightsbridge) Limited' (incorporated 1969), which is why Companies House shows an incorporation date decades before Tandem's own 2013 founding. Confirmed via Companies House (previous-names history) and cross-checked against the FRN in Banks List 2608.xlsx.
+RESTATEMENT NOTE: FY2022's Balance Sheet, Profit &amp; Loss and Statement of Changes in Equity figures shown here are Tandem Bank Limited's own AS-ORIGINALLY-PUBLISHED figures (from the FY2022 Annual Report and Accounts), not the later FY2023 Annual Report's restated FY2022 comparative column (which reclassified certain effective interest rate balances and reflected motor finance hire purchase receivables as secured rather than unsecured lending - Note 2 of the FY2023 Annual Report). This creates a genuine, documented, non-plugged break at the FY2022/FY2023 boundary on the Statement of Changes in Equity sheet: FY2022's own closing Total equity (£115,178k) does not equal the FY2023 Annual Report's restated FY2023 opening balance (£115,535k, a £357k difference, itself split into a +£1,737k Other Reserves capital-contribution reclassification and a -£1,380k Retained earnings adjustment) - both figures are shown, connected by an explicit 'Restatement (per Note 2 of the FY2023 Annual Report)' row rather than silently smoothed over. The same restatement affects Loans and advances to customers on the Balance Sheet (FY2022 shown here as £1,078,369k as originally reported vs. £1,080,282k in the FY2023 Annual Report's restated comparative) and the FY2022 Profit &amp; Loss (originally reported: Interest income £74,932k, Loss on operating activities before tax £(6,933)k, Loss for the year £(1,654)k; FY2023 Annual Report's restated comparative: Interest income £72,374k, Loss before tax £(9,491)k, Loss for the year £(4,212)k).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A43:F43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2512,16 +6269,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2532,433 +6289,433 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — CET1 Capital</t>
+          <t>Tandem Bank Limited — Asset Quality</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, £'000</t>
+          <t>Bank (Company-only) basis, £'000. NPL/coverage ratios derived from the figures above.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>168224</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>165574</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>150158</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>119883</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>39742</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Gross Loans and Advances to Customers by Product</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>First charge mortgages</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>126826</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>156342</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>213554</v>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Second charge mortgages</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>517524</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>508609</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>580850</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Motor finance hire purchase receivables</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>323027</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>223688</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>115554</v>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Secured lending (product-level split not disclosed pre-FY2023 - see source note)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n">
+        <v>692093</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>262023</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Unsecured lending</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>366008</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>373406</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>407597</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>434784</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>182894</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Gross Loans and Advances to Customers</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1333385</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1262045</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1317555</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1126877</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>444917</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Credit Quality Analysis</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Total gross impaired loans</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>135788</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>109289</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>71399</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>47188</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>8443</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Past due but not impaired</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1289</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>16658</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>17441</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>11604</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>13074</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Neither past due nor impaired</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1196308</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1136098</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1228715</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1068085</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>423400</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total gross amount due</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1333385</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1262045</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1317555</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1126877</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>444917</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Impairment and Coverage</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Provision for impairment</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-53848</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-40875</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-30460</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-26381</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-5834</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Fair value adjustments (hedge accounting / acquisition of loan portfolio)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>5364</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-1914</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-6199</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-22127</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-2238</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Net Loans and Advances to Customers</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1284901</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1219256</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1280896</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1078369</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>436845</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>NPL ratio (impaired loans / gross loans)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>10.18%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>8.66%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>5.42%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>4.19%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>1.90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Coverage ratio (provision / impaired loans)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>39.65%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>37.40%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>42.66%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>55.90%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>69.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="300" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Tandem Bank Limited's own (Company-only, not TML Group) figures, £'000:
+FY2025/FY2024: Annual Report and Accounts for the year ended 31 December 2025, Note 11 (Loans and Advances to Customers) and Note 25.1(ii) (Credit Risk - Credit Quality Analysis) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2023: Annual Report and Accounts for the year ended 31 December 2023, Note 11 and Note 24.1(ii) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2022: Annual Report and Accounts for the year ended 31 December 2022, Note 14 and Note 29.1(ii) - as originally reported, NOT the FY2023 Annual Report's later restated comparative - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+FY2021: as reported in the FY2022 Annual Report's own comparative column, Note 14 and Note 29.1(ii); cross-checked against the FY2021 Annual Report's own Note 11 and Note 25.1 figures and matched exactly - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
+The product breakdown (First/Second charge mortgages, Motor finance hire purchase receivables, Unsecured lending) was only introduced from the FY2023 Annual Report onward; FY2022 and FY2021 are shown here on the Bank's own then-current Secured/Unsecured split (blank cells above indicate the sub-product breakdown did not exist that year, not a missing figure - the Unsecured lending row and product-level Secured total both tie to Gross Loans and Advances to Customers for those years). 'Fair value adjustments' combines the hedge-accounting fair value adjustment and, from FY2021 onward, the acquisition-of-loan-portfolio fair value adjustment recognised on the Bank's 2024 repurchase of a mortgage portfolio from a related-party SPE (see Note 11 of the FY2025 Annual Report) - both are disclosed as a single combined 'Fair value adjustment for portfolio hedged risk' line pre-FY2025.
+ENTITY NOTE: 'Tandem Bank Limited' (company number 00955491, FRN 204479) is the PRA-authorised entity built here. It is NOT the same company as 'Tandem Money Limited' (company number 08628614) - a related, similarly-named entity that briefly used the name 'Tandem Bank Limited' itself from Dec 2015-May 2017 before becoming Tandem Money Limited (TML), the non-bank holding company that today sits above Tandem Bank Limited (TBL) in the group structure. Company 00955491 was previously 'Harrods Bank Limited' (renamed 12 Jan 2018) - Tandem acquired Harrods Bank's banking licence in 2017 to become a PRA-authorised deposit-taker quickly; it traces further back to 'Harrods Trust Limited' and, before that, 'Harrods (Knightsbridge) Limited' (incorporated 1969), which is why Companies House shows an incorporation date decades before Tandem's own 2013 founding. Confirmed via Companies House (previous-names history) and cross-checked against the FRN in Banks List 2608.xlsx.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tandem Bank Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TML Group basis, % of RWEA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.53%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.40%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tandem Bank Limited — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TML Group basis, £'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>168224</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>165574</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>150158</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>119883</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>39742</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Tier 1 Capital = CET1 Capital every year through FY2022 (no AT1 instruments); AT1 capital was first issued in FY2023 but is included within Total Capital, not Tier 1, per the Group's own KM1 template (rows 1 and 2 are identical every year) - Total Capital is the row where AT1/T2 shows up as a difference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tandem Bank Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TML Group basis, % of RWEA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.53%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.40%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2984,7 +6741,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Total Capital</t>
+          <t>Tandem Bank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -3030,17 +6787,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>196155</v>
+        <v>168224</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>192343</v>
+        <v>165574</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>175438</v>
+        <v>150158</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>119883</v>
@@ -3090,7 +6847,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Total Capital Ratio</t>
+          <t>Tandem Bank Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3136,22 +6893,22 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>18.11%</t>
+          <t>15.53%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>20.21%</t>
+          <t>17.40%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -3192,7 +6949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3206,7 +6963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Total RWAs</t>
+          <t>Tandem Bank Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3252,27 +7009,34 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted assets (RWEA)</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1083333</v>
+        <v>168224</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>951607</v>
+        <v>165574</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>931650</v>
+        <v>150158</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>790158</v>
+        <v>119883</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>280843</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+        <v>39742</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Tier 1 Capital = CET1 Capital every year through FY2022 (no AT1 instruments); AT1 capital was first issued in FY2023 but is included within Total Capital, not Tier 1, per the Group's own KM1 template (rows 1 and 2 are identical every year) - Total Capital is the row where AT1/T2 shows up as a difference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
 FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
@@ -3285,8 +7049,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/TANDEM FINANCIALS.xlsx
+++ b/banks/TANDEM FINANCIALS.xlsx
@@ -4106,7 +4106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -4244,7 +4244,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Debt securities</t>
+          <t>Total debt securities</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -4266,409 +4266,491 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Debt securities at amortised cost (Mortgage Backed Loan Notes Class A + Vertical Risk Retention Notes)</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>6383</v>
+        <v>300970</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>11304</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>24353</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>29592</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>2358</v>
-      </c>
+        <v>213670</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Equity shares</t>
+          <t>Debt securities available-for-sale (at market value)</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3667</v>
+        <v>253688</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3533</v>
+        <v>156481</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2758</v>
+        <v>56609</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2309</v>
+        <v>91210</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1970</v>
+        <v>30215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Other assets</t>
+          <t>UK Government securities (part of Debt securities)</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>11395</v>
+        <v>31269</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>10296</v>
+        <v>0</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>27830</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>23287</v>
+        <v>19960</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5639</v>
+        <v>5078</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Prepayments and accrued income</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
+          <t>Other debt securities (supranational, European and UK financial institutions, mortgage-backed loan notes)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>523389</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>370151</v>
+      </c>
       <c r="D12" s="6" t="n">
-        <v>493</v>
+        <v>56609</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>500</v>
+        <v>71250</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>4</v>
+        <v>25137</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Deferred tax asset</t>
+          <t>Derivative financial instruments</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>8816</v>
+        <v>6383</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>10295</v>
+        <v>11304</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>10236</v>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
+        <v>24353</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>29592</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2358</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>2489828</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>3155197</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>3859400</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>1926197</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>853719</v>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Equity shares</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>3667</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>3533</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2758</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2309</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1970</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>11395</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>10296</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>27830</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>23287</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>5639</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Deposits by banks / Borrowings from banks</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>10113</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>23798</v>
-      </c>
+          <t>Prepayments and accrued income</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n">
-        <v>30934</v>
+        <v>493</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>43527</v>
+        <v>500</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>40013</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Customer accounts</t>
+          <t>Deferred tax asset</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>2260738</v>
+        <v>8816</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2916365</v>
+        <v>10295</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3639407</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>1754868</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>771161</v>
-      </c>
+        <v>10236</v>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Derivative financial instruments</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>4988</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>2503</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>11197</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>7057</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>89</v>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2489828</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3155197</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3859400</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1926197</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>853719</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Other liabilities</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>6467</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>15529</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>1613</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>5162</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>522</v>
-      </c>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Accruals and deferred income</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
+          <t>Deposits by banks / Borrowings from banks</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>10113</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>23798</v>
+      </c>
       <c r="D20" s="6" t="n">
-        <v>735</v>
+        <v>30934</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>405</v>
+        <v>43527</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>314</v>
+        <v>40013</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Subordinated liabilities</t>
+          <t>Customer accounts</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>19592</v>
+        <v>2260738</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>19323</v>
+        <v>2916365</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>18943</v>
-      </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
+        <v>3639407</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1754868</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>771161</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Total Liabilities</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>2301898</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>2977518</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>3702829</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>1811019</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>812099</v>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>4988</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>2503</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>11197</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>7057</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>6467</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>15529</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>1613</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>5162</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>522</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Called-up share capital</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>200999</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>192999</v>
-      </c>
+          <t>Accruals and deferred income</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n">
-        <v>187999</v>
+        <v>735</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>152339</v>
+        <v>405</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>75875</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Other reserves</t>
+          <t>Subordinated liabilities</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>85444</v>
+        <v>19592</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>86998</v>
+        <v>19323</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>82924</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>80051</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>80051</v>
-      </c>
+        <v>18943</v>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Retained reserves (Available for sale reserve + Retained earnings/(losses))</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>-98513</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>-102318</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>-114352</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>-117212</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>-114306</v>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2301898</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>2977518</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3702829</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1811019</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>812099</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Called-up share capital</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>200999</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>192999</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>187999</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>152339</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>75875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>85444</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>86998</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>82924</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>80051</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>80051</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Retained reserves (Available for sale reserve + Retained earnings/(losses))</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-98513</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-102318</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>-114352</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>-117212</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-114306</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B31" s="5" t="n">
         <v>187930</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C31" s="5" t="n">
         <v>177679</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D31" s="5" t="n">
         <v>156571</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E31" s="5" t="n">
         <v>115178</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F31" s="5" t="n">
         <v>41620</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Total Liabilities and Equity</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B32" s="5" t="n">
         <v>2489828</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C32" s="5" t="n">
         <v>3155197</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D32" s="5" t="n">
         <v>3859400</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E32" s="5" t="n">
         <v>1926197</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F32" s="5" t="n">
         <v>853719</v>
       </c>
     </row>
-    <row r="30" ht="280" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="34" ht="280" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Tandem Bank Limited's own (Company-only, not TML Group) figures, £'000:
 FY2025: Annual Report and Accounts for the year ended 31 December 2025, p.25 (2025)/26 (2024 comparative) (Statement of Financial Position), p.24 (2025)/25 (2024 comparative) (Income Statement and Statement of Other Comprehensive Income), p.26 (2025)/27 (2024 comparative) (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
@@ -4677,13 +4759,14 @@
 FY2022: Annual Report and Accounts for the year ended 31 December 2022, p.43 (Statement of Financial Position), p.42 (Income Statement and Statement of Other Comprehensive Income), p.44 (Statement of Changes in Equity) - as originally reported, NOT the FY2023 Annual Report's later restated comparative - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
 FY2021: Annual Report and Accounts for the year ended 31 December 2021, p.46 (Income Statement and Statement of Other Comprehensive Income), p.47 (Statement of Financial Position), p.48 (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
 ENTITY NOTE: 'Tandem Bank Limited' (company number 00955491, FRN 204479) is the PRA-authorised entity built here. It is NOT the same company as 'Tandem Money Limited' (company number 08628614) - a related, similarly-named entity that briefly used the name 'Tandem Bank Limited' itself from Dec 2015-May 2017 before becoming Tandem Money Limited (TML), the non-bank holding company that today sits above Tandem Bank Limited (TBL) in the group structure. Company 00955491 was previously 'Harrods Bank Limited' (renamed 12 Jan 2018) - Tandem acquired Harrods Bank's banking licence in 2017 to become a PRA-authorised deposit-taker quickly; it traces further back to 'Harrods Trust Limited' and, before that, 'Harrods (Knightsbridge) Limited' (incorporated 1969), which is why Companies House shows an incorporation date decades before Tandem's own 2013 founding. Confirmed via Companies House (previous-names history) and cross-checked against the FRN in Banks List 2608.xlsx.
-RESTATEMENT NOTE: FY2022's Balance Sheet, Profit &amp; Loss and Statement of Changes in Equity figures shown here are Tandem Bank Limited's own AS-ORIGINALLY-PUBLISHED figures (from the FY2022 Annual Report and Accounts), not the later FY2023 Annual Report's restated FY2022 comparative column (which reclassified certain effective interest rate balances and reflected motor finance hire purchase receivables as secured rather than unsecured lending - Note 2 of the FY2023 Annual Report). This creates a genuine, documented, non-plugged break at the FY2022/FY2023 boundary on the Statement of Changes in Equity sheet: FY2022's own closing Total equity (£115,178k) does not equal the FY2023 Annual Report's restated FY2023 opening balance (£115,535k, a £357k difference, itself split into a +£1,737k Other Reserves capital-contribution reclassification and a -£1,380k Retained earnings adjustment) - both figures are shown, connected by an explicit 'Restatement (per Note 2 of the FY2023 Annual Report)' row rather than silently smoothed over. The same restatement affects Loans and advances to customers on the Balance Sheet (FY2022 shown here as £1,078,369k as originally reported vs. £1,080,282k in the FY2023 Annual Report's restated comparative) and the FY2022 Profit &amp; Loss (originally reported: Interest income £74,932k, Loss on operating activities before tax £(6,933)k, Loss for the year £(1,654)k; FY2023 Annual Report's restated comparative: Interest income £72,374k, Loss before tax £(9,491)k, Loss for the year £(4,212)k).</t>
+RESTATEMENT NOTE: FY2022's Balance Sheet, Profit &amp; Loss and Statement of Changes in Equity figures shown here are Tandem Bank Limited's own AS-ORIGINALLY-PUBLISHED figures (from the FY2022 Annual Report and Accounts), not the later FY2023 Annual Report's restated FY2022 comparative column (which reclassified certain effective interest rate balances and reflected motor finance hire purchase receivables as secured rather than unsecured lending - Note 2 of the FY2023 Annual Report). This creates a genuine, documented, non-plugged break at the FY2022/FY2023 boundary on the Statement of Changes in Equity sheet: FY2022's own closing Total equity (£115,178k) does not equal the FY2023 Annual Report's restated FY2023 opening balance (£115,535k, a £357k difference, itself split into a +£1,737k Other Reserves capital-contribution reclassification and a -£1,380k Retained earnings adjustment) - both figures are shown, connected by an explicit 'Restatement (per Note 2 of the FY2023 Annual Report)' row rather than silently smoothed over. The same restatement affects Loans and advances to customers on the Balance Sheet (FY2022 shown here as £1,078,369k as originally reported vs. £1,080,282k in the FY2023 Annual Report's restated comparative) and the FY2022 Profit &amp; Loss (originally reported: Interest income £74,932k, Loss on operating activities before tax £(6,933)k, Loss for the year £(1,654)k; FY2023 Annual Report's restated comparative: Interest income £72,374k, Loss before tax £(9,491)k, Loss for the year £(4,212)k).
+DEBT SECURITIES BREAKDOWN NOTE: the amortised-cost/available-for-sale and UK Government/other sub-rows beneath 'Total debt securities' are drawn from the Bank's own 'Debt Securities' note, not estimated: FY2025/FY2024 from Note 12 (Debt Securities), p.42 of the FY2025 Annual Report - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history; FY2023/FY2022 (as originally reported in that year's own filing) from Note 12, p.50 of the FY2023 Annual Report - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history; FY2021 from Note 15, p.61 of the FY2022 Annual Report (that filing's own '2021' comparative column) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history. From FY2025, the note also splits out amortised-cost holdings (Mortgage Backed Loan Notes Class A and Vertical Risk Retention Notes issued by the Bank's own securitisation vehicles, Fylde Funding 2025-1 PLC and predecessors) that did not exist in FY2021-FY2023, when the entire debt securities book was held available-for-sale at market value for liquidity purposes; FY2024's 'UK Government' leg is a genuine disclosed nil (the note shows '-'), not a missing value.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A34:F34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/TANDEM FINANCIALS.xlsx
+++ b/banks/TANDEM FINANCIALS.xlsx
@@ -3392,10 +3392,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3411,96 +3411,235 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group (consolidated) basis, £'000, all directly disclosed. FY2022-FY2025 follow the UK OV1 template; FY2021 predates it and uses a different, coarser category split - see the two SECTION blocks below and the sources note. Each year's TOTAL matches the Total RWAs sheet's figure for that year exactly.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>RWA Breakdown</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: TML's Pillar 3 Disclosures do not include a UK OV1-style RWA breakdown-by-risk-category table in any year FY2021-FY2025 (all 4 available editions checked directly - each is a short document, 9-15 pages, consistent with the Group's stated 'small, non-complex' institution status under UK CRR Article 4(145) and the reduced Pillar 3 disclosure regime of Article 433(b), the same basis already noted for MREL Ratio's non-disclosure).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>UK OV1 — Overview of risk weighted exposure amounts (TML GROUP, CONSOLIDATED)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>870361</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>786363</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>816990</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>699002</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR) (includes credit valuation adjustment - see sources note)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>6519</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4759</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>8096</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>6168</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Securitisation exposures in the non-trading book (after the cap)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>42004</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>29907</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>164449</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>130578</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>106564</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>84988</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total risk weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1083333</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>951607</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>931650</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>790158</v>
+      </c>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Pillar 1 Capital Requirement table (TML GROUP, CONSOLIDATED, as disclosed)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Total credit risk</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n">
+        <v>251021</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>26340</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Credit valuation adjustment</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>3482</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total Pillar 1 / risk weighted assets</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n">
+        <v>280843</v>
+      </c>
+    </row>
+    <row r="16" ht="220" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Sources - TML Group (consolidated) basis, £'000, all figures DIRECTLY DISCLOSED (no derivation needed) - matching the Total RWAs sheet's own figures for every year exactly:
+FY2025 &amp; FY2024 (comparative column): TML Pillar 3 Disclosures, 31 December 2025, p.5, Table 'UK OV1 - Overview of risk weighted exposure amounts' - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024 (own-year column, used above) &amp; FY2023 (comparative column): TML Pillar 3 Disclosures, 31 December 2024, p.5, Table 'UK OV1 - Overview of risk weighted exposure amounts' - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023 (own-year column, used above) &amp; FY2022 (comparative column): TML Pillar 3 Disclosures, 31 December 2023, p.4, Table 'UK OV1 - Overview of risk weighted exposure amounts' - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.22, 'Pillar 1 Capital Requirement' table (its own dedicated 'Risk Weighted Assets' column, not the adjacent 'Pillar 1 Requirement' capital column - no x12.5 derivation needed) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+CATEGORY NOTE: FY2022-FY2025 follow the UK OV1 template (Credit Risk excl. CCR / Counterparty Credit Risk - the CCR figure itself already comprises 'of which OEM' and 'of which CVA' sub-lines per the source table's own rows 7/UK8b, so CVA is not broken out as a separate summed row here to avoid double-counting / Securitisation exposures in the non-trading book, first appearing FY2024 / Operational Risk). FY2021 predates TML's adoption of the OV1 template and instead discloses a Standardised-Exposure-Class Pillar 1 table with a coarser split (Total Credit Risk / Operational Risk / Credit Valuation Adjustment, with CVA shown as its own top-level category rather than nested under CCR, and no separate CCR line at all) - shown as its own SECTION block rather than blended into the OV1 rows above. Every year's TOTAL below reconciles exactly to the Total RWAs sheet's own figure for that year (FY2025: 1,083,333; FY2024: 951,607; FY2023: 931,650; FY2022: 790,158; FY2021: 280,843).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/TANDEM FINANCIALS.xlsx
+++ b/banks/TANDEM FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2948,7 +2949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2962,14 +2963,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Tier 1 Ratio</t>
+          <t>Tandem Bank Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, % of RWEA</t>
+          <t>TML Group basis, £'000</t>
         </is>
       </c>
     </row>
@@ -3008,37 +3009,34 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.53%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.40%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>168224</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>165574</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>150158</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>119883</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>39742</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Tier 1 Capital = CET1 Capital every year through FY2022 (no AT1 instruments); AT1 capital was first issued in FY2023 but is included within Total Capital, not Tier 1, per the Group's own KM1 template (rows 1 and 2 are identical every year) - Total Capital is the row where AT1/T2 shows up as a difference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
 FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
@@ -3051,8 +3049,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3078,14 +3077,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Total Capital</t>
+          <t>Tandem Bank Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, £'000</t>
+          <t>TML Group basis, % of RWEA</t>
         </is>
       </c>
     </row>
@@ -3124,23 +3123,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>196155</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>192343</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>175438</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>119883</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>39742</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.53%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.40%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -3184,14 +3193,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Total Capital Ratio</t>
+          <t>Tandem Bank Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, % of RWEA</t>
+          <t>TML Group basis, £'000</t>
         </is>
       </c>
     </row>
@@ -3230,33 +3239,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>18.11%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.21%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>18.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>196155</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>192343</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>175438</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>119883</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>39742</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -3300,14 +3299,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Total RWAs</t>
+          <t>Tandem Bank Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, £'000</t>
+          <t>TML Group basis, % of RWEA</t>
         </is>
       </c>
     </row>
@@ -3346,23 +3345,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted assets (RWEA)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1083333</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>951607</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>931650</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>790158</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>280843</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>18.11%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.21%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -3387,6 +3396,112 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted assets (RWEA)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1083333</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>951607</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>931650</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>790158</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>280843</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3645,7 +3760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3786,170 +3901,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tandem Bank Limited — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TML Group basis, £'000 / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total high-quality liquid assets (HQLA), weighted value (average)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1148813</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1927554</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1786879</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>329806</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows, adjusted value</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>258152</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>359743</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>281464</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>103147</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>443.40%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>534.75%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>636.0%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>314.1%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>331%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2022-FY2025 LCR is a simple average of monthly liquidity positions during the calendar year (per each report's own footnote). FY2021 used a different methodology (simple average of month-end observations over the trailing 12 months up to each quarter-end); the Group's FY2021 report only tabulates quarterly LCR values (31%: Dec '21 = 331%, Sep '21 = 394%, Jun '21 = 709%, Mar '21 = 1,832%) rather than one annual figure - the 31 Dec 2021 (year-end) value is shown here for comparability, but the two methodologies are not identical so a direct FY2021-to-FY2022 LCR comparison should be treated with caution. No HQLA/cash-outflow £ breakdown was found for FY2021 (only the % ratio was tabulated).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="170" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3975,7 +3926,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — NSFR</t>
+          <t>Tandem Bank Limited — LCR</t>
         </is>
       </c>
     </row>
@@ -4021,79 +3972,79 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding</t>
+          <t>Total high-quality liquid assets (HQLA), weighted value (average)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2560820</v>
+        <v>1148813</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3156347</v>
+        <v>1927554</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3142854</v>
+        <v>1786879</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1447618</v>
+        <v>329806</v>
       </c>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total required stable funding</t>
+          <t>Total net cash outflows, adjusted value</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1320668</v>
+        <v>258152</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1199958</v>
+        <v>359743</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1156379</v>
+        <v>281464</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>922410</v>
+        <v>103147</v>
       </c>
       <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>NSFR ratio (%)</t>
+          <t>Liquidity Coverage Ratio (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>194.30%</t>
+          <t>443.40%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>263.10%</t>
+          <t>534.75%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>270.6%</t>
+          <t>636.0%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>155.5%</t>
+          <t>314.1%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>331%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: NSFR not disclosed for FY2021 - not yet part of TML's Pillar 3 template that year (consistent with the UK NSFR requirement not applying to reporting periods that early elsewhere in this project, e.g. Zopa).</t>
+          <t>Note: FY2022-FY2025 LCR is a simple average of monthly liquidity positions during the calendar year (per each report's own footnote). FY2021 used a different methodology (simple average of month-end observations over the trailing 12 months up to each quarter-end); the Group's FY2021 report only tabulates quarterly LCR values (31%: Dec '21 = 331%, Sep '21 = 394%, Jun '21 = 709%, Mar '21 = 1,832%) rather than one annual figure - the 31 Dec 2021 (year-end) value is shown here for comparability, but the two methodologies are not identical so a direct FY2021-to-FY2022 LCR comparison should be treated with caution. No HQLA/cash-outflow £ breakdown was found for FY2021 (only the % ratio was tabulated).</t>
         </is>
       </c>
     </row>
@@ -4120,6 +4071,170 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group basis, £'000 / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2560820</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3156347</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3142854</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1447618</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1320668</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1199958</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1156379</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>922410</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>194.30%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>263.10%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>270.6%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>155.5%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: NSFR not disclosed for FY2021 - not yet part of TML's Pillar 3 template that year (consistent with the UK NSFR requirement not applying to reporting periods that early elsewhere in this project, e.g. Zopa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6949,10 +7064,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -6963,21 +7078,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — CET1 Capital</t>
+          <t>Tandem Bank Limited — KM1 Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, £'000</t>
+          <t>TML Group's own published 'Key metrics table (UK KM1)', reproduced in the Group's row order with its own row numbers. TML GROUP CONSOLIDATED basis (TML + Tandem Bank Limited + Allium Lending Group), not Bank solo. Amounts in £'000, ratios as printed. Only the FY2023, FY2024 and FY2025 editions carry the template - FY2022 has no edition of its own and FY2021's edition does not use the template.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -7007,43 +7122,684 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AVAILABLE OWN FUNDS (£'000)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1    Common Equity Tier 1 (CET1) Capital</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>168224</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="6" t="n">
         <v>165574</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D5" s="6" t="n">
         <v>150158</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>119883</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>39742</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2    Tier 1 Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>168224</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>165574</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>150158</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3    Total Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>196155</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>192343</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>175438</v>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>RISK-WEIGHTED EXPOSURE AMOUNTS (RWEA) (£'000)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4    Total Risk Weighted Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1083333</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>951607</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>931650</v>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>CAPITAL RATIOS (as percentage of RWEA)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>5    Common Equity Tier 1 Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>15.53%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>17.40%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6    Tier 1 Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>15.53%</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>17.40%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7    Total Capital Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>18.11%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>20.21%</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ADDITIONAL OWN FUNDS REQUIREMENTS BASED ON SREP (as percentage of RWEA)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a    Additional CET1 SREP Requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.04%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1.04%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>UK 7b    Additional AT1 SREP Requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>UK 7c    Additional T2 SREP Requirements (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d    Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>9.84%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>9.84%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>10.6%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>COMBINED BUFFER REQUIREMENT (as percentage of RWEA)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>8    Capital Conservation Buffer (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>9    Institution Specific Countercyclical Capital Buffer (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>11    Combined Buffer Requirement (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>4.45%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a    Overall Capital Requirement (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>14.30%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>14.29%</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>12    CET1 available after meeting total SREP Own Funds Requirements (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>9.99%</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>14.68%</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>12.9%</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>LEVERAGE RATIO</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>13    Total Exposure Measure excluding Claims on Central Banks (£'000)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1860727</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>1652240</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1458860</v>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>14    Leverage Ratio excluding Claims on Central Banks (%)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>9.04%</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>10.02%</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>LIQUIDITY COVERAGE RATIO</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>15    Total High-Quality Liquid Assets (HQLA) (Weighted Value-Average) (£'000)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>1148813</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>1927554</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>1786879</v>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>UK 16a    Cash Outflows – Total Weighted Value (£'000)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>327080</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>424591</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>348061</v>
+      </c>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>UK 16b    Cash Inflows – Total Weighted Value (£'000)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>68928</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>64311</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>66597</v>
+      </c>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>16    Total Net Cash Outflows (Adjusted Value) (£'000)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>258152</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>359743</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>281464</v>
+      </c>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>17    Liquidity Coverage Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>443.40%</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>534.75%</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>636.0%</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>NET STABLE FUNDING RATIO</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>18    Total Available Stable Funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>2560820</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>3156347</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>3142854</v>
+      </c>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>19    Total Required Stable Funding (£'000)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>1320668</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>1199958</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>1156379</v>
+      </c>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>20    NSFR Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>194.30%</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>263.10%</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>270.6%</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="39" ht="300" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) GROUP consolidated basis (TML + Tandem Bank Limited + Allium Lending Group Limited), NOT Tandem Bank Limited solo. The Group's own 'Key metrics table (UK KM1)', section 2 'Key Metrics', taken from EACH YEAR'S OWN edition rather than from any later edition's comparative column:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+LATEST-EDITION CHECK, 2026-09-16, ON TANDEM'S OWN SITE. www.tandem.co.uk/newsroom was fetched directly (HTTP 200, 178,512 bytes) and every PDF link on it extracted. It lists exactly three Pillar 3 documents - 'Pillar 3 Disclosures 31 December 2023', '...31 December 2024' and '...31 December 2025' - plus the TML Annual Report and Accounts FY23/FY24/FY25. THE NEWEST PILLAR 3 IS THE 31 DECEMBER 2025 EDITION, which this workbook already holds, so no year is added. (Tandem's year-end is 31 December, so an FY2026 edition cannot exist before 2027.) All four PDFs used here were re-downloaded the same day and verified by HTTP status, Content-Type application/pdf and %PDF magic bytes.
+RESTATEMENTS FOUND AND DELIBERATELY NOT USED - THIS IS WHY EACH COLUMN COMES FROM ITS OWN EDITION.
+  * Row 12, FY2024. The FY2024 edition prints 14.68% for 31 Dec '24. The FY2025 edition's 31 Dec '24 comparative prints 11.86% and footnotes it '2024 ratio restated'. 14.68% is shown above, per this workbook's convention; the restated figure remains visible in the FY2025 document.
+  * Rows 13 and 14, FY2023. The FY2023 edition prints an exposure measure of 1,458,860 and a leverage ratio of 9.8%. The FY2024 edition's 31 Dec '23 comparative prints 1,529,033 and 9.82%, both footnoted 'Restated'. The FY2023 edition's own figures are shown above.
+  * The whole FY2023 SREP/buffer block is printed to one decimal place in its own edition (UK 7a 1.5%, UK 7b 0.5%, UK 7c 0.7%, UK 7d 10.6%, row 9 1.9%, row 11 4.4%, UK 11a 15.0%, row 12 12.9%) and to two decimals in the FY2024 edition's comparative (1.45% / 0.48% / 0.65% / 10.58% / 1.94% / 4.44% / 15.02% / 12.88%). These are not rounding artefacts to be tidied: PRECISION IS THE BANK'S OWN and the FY2023 column above keeps the FY2023 edition's one-decimal house style throughout, including LCR 636.0% (534.75%-style two-decimal printing starts with the FY2024 edition) and NSFR 270.6%.
+FY2022 IS BLANK, AND A FULL FY2022 KM1 COLUMN DOES EXIST - AS THE FY2023 EDITION'S COMPARATIVE - AND IS DELIBERATELY NOT USED. No standalone Pillar 3 edition for 31 December 2022 was ever published: Tandem's own newsroom (checked 2026-09-16, see above) lists 2023, 2024 and 2025 only, and the 2021 edition sits on the older assets.website-files.com CDN and is no longer linked from the newsroom at all. Every column on this sheet comes from the edition in which that year is the reporting year, and there is no such edition for FY2022. For the record, the FY2023 edition's '31 Dec '22' column prints: CET1 / Tier 1 / Total capital all 119,883; RWEA 790,158; CET1, Tier 1 and Total capital ratios all 15.2%; UK 7a-7d 1.5% / 0.5% / 0.7% / 10.6%; row 8 2.5%; row 9 1.0%; row 11 3.5%; UK 11a 14.1%; row 12 9.2%; row 13 1,401,205; row 14 8.8%; row 15 329,806; UK 16a 158,136; UK 16b 54,989; row 16 103,147; row 17 314.1%; row 18 1,447,618; row 19 922,410; row 20 155.5%. Those figures DO appear on this workbook's single-metric sheets, captioned there as coming from the FY2023 edition's comparative column - that is a different presentation from reproducing a template Tandem never published for that date, which is why they are not carried here.
+FY2021 IS BLANK BECAUSE THE TEMPLATE IS NOT USED, NOT BECAUSE NO PILLAR 3 EXISTS. TML published a full Pillar 3 report for 31 December 2021 (https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf; re-read in full 2026-09-16, 139,114 characters of clean text). It contains no KM1. Its section 4 'Capital Disclosures' (printed p.21, located from the document's OWN table of contents rather than by scanning for digits) opens with a table headed 'Key Regulatory Metrics' - but that table has exactly FOUR unnumbered rows (CET1 Capital 39,742; Total Risk Weighted Assets 280,843; CET1 Capital Ratio 14.2%; Leverage Ratio 4.6%, with a 31 December 2020 comparative). Four rows with no SREP block, no buffer block, no LCR rows and no NSFR rows is a different and much shorter table, not an unnumbered KM1, so mapping it onto template row numbers would invent a correspondence Tandem never published. Its figures appear on the single-metric sheets instead, captioned as their own edition printed them. Supporting whole-document counts, all case-insensitive, on an extraction shown to be RICH on neighbouring terms ('capital' 90, 'ratio' 120, 'cet1' 15, 'buffer' 22, 'leverage' 14) so the zeroes are facts about the document and not a failed instrument: 'km1' 0, 'srep' 0, 'UK 7a' 0, 'available own funds' 0, 'risk-weighted exposure' 0.
+ROWS TANDEM DOES NOT PRINT ARE ABSENT, NOT ZERO. All three editions omit row 10 (G-SII buffer), UK 8a, UK 9a and UK 10a, and rows 21-23, entirely - there is no cell, no dash and no zero to reproduce - so they are not shown here at all rather than shown blank.
+NO LEVERAGE BASIS BREAK TO CARRY. Tandem's first KM1 edition is FY2023, already after the 1 January 2022 UK leverage change, so rows 13/14 carry the 'excluding Claims on Central Banks' caption in all three editions and need only one caption block. (The Group states in each edition that it remains OUTSIDE the scope of the full UK Leverage Ratio Framework.) The unit is £'000 in all three editions, so no two-unit caption block is needed either.
+THE TEMPLATE'S OWN FOOTNOTES, WHICH QUALIFY ROWS 15-20 IN EVERY EDITION: the LCR block is 'calculated as average of monthly liquidity positions during' the year and the NSFR block 'as average of quarterly NSFR positions during' the year - so rows 15-20 are AVERAGES, not point-in-time year-end figures, while rows 1-14 are point-in-time. Row 12 is defined by the Group as 'CET1 ratio less the minimum amount of CET1 required to meet the total SREP own funds requirement (56.25% of Pillar 1 and Pillar 2A capital requirements)', and the SREP block footnote reads 'Of which 56.25% of CET1 capital, 43.75% of AT1 capital and 25% of Tier 2 capital'.
+ENTITY NOTE: 'Tandem Bank Limited' (company number 00955491, FRN 204479) is the PRA-authorised entity built here. It is NOT the same company as 'Tandem Money Limited' (company number 08628614) - a related, similarly-named entity that briefly used the name 'Tandem Bank Limited' itself from Dec 2015-May 2017 before becoming Tandem Money Limited (TML), the non-bank holding company that today sits above Tandem Bank Limited (TBL) in the group structure. Company 00955491 was previously 'Harrods Bank Limited' (renamed 12 Jan 2018) - Tandem acquired Harrods Bank's banking licence in 2017 to become a PRA-authorised deposit-taker quickly; it traces further back to 'Harrods Trust Limited' and, before that, 'Harrods (Knightsbridge) Limited' (incorporated 1969), which is why Companies House shows an incorporation date decades before Tandem's own 2013 founding. Confirmed via Companies House (previous-names history) and cross-checked against the FRN in Banks List 2608.xlsx.
+PILLAR 3 BASIS NOTE: this sheet is TML GROUP consolidated, whereas the four statement sheets in this workbook are Tandem Bank Limited solo. Tandem does not publish a Bank-only Pillar 3 breakout, so the basis mismatch is the group's own and cannot be closed.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7069,14 +7825,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — CET1 Ratio</t>
+          <t>Tandem Bank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, % of RWEA</t>
+          <t>TML Group basis, £'000</t>
         </is>
       </c>
     </row>
@@ -7115,33 +7871,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.53%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.40%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>168224</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>165574</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>150158</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>119883</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>39742</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -7171,7 +7917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7185,14 +7931,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Tier 1 Capital</t>
+          <t>Tandem Bank Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, £'000</t>
+          <t>TML Group basis, % of RWEA</t>
         </is>
       </c>
     </row>
@@ -7231,34 +7977,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>168224</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>165574</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>150158</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>119883</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>39742</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Tier 1 Capital = CET1 Capital every year through FY2022 (no AT1 instruments); AT1 capital was first issued in FY2023 but is included within Total Capital, not Tier 1, per the Group's own KM1 template (rows 1 and 2 are identical every year) - Total Capital is the row where AT1/T2 shows up as a difference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.53%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.40%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
 FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
@@ -7271,9 +8020,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/TANDEM FINANCIALS.xlsx
+++ b/banks/TANDEM FINANCIALS.xlsx
@@ -1730,6 +1730,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4328,7 +4329,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: MREL is not disclosed in any of TML's Pillar 3 Disclosures FY2021-FY2025. The Group states (FY2023 Pillar 3 Disclosures, Overview) that it qualifies as a 'small, non-complex' institution under UK CRR Article 4(145) and follows the reduced Pillar 3 disclosure regime of Article 433(b) - consistent with, though not an explicit stated reason for, the absence of any MREL figure.</t>
+          <t>Note: MREL is not disclosed in any of TML's Pillar 3 Disclosures FY2021-FY2025. The Group states (FY2023 Pillar 3 Disclosures, Overview) that it qualifies as a 'small, non-complex' institution under UK CRR Article 4(145) and follows the reduced Pillar 3 disclosure regime of Article 433(b) - consistent with, though not an explicit stated reason for, the absence of any MREL figure. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): the missing stated reason is now supplied from outside the bank's own documents. The Bank of England's 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures (2023, 2024, 2025 and 2026 editions, at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt;) contain 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated', in the BoE's own words, and Tandem is named in none of them. So the absence of an MREL figure reflects there being no MREL above minimum capital requirement to report, not a gap in the reduced Article 433(b) disclosure set. The BoE publishes the requirement, not the ratio, so nothing from that table is transcribed here.</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -6338,7 +6339,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bank (Company-only) basis, £'000. FY2023-FY2025 blank - see source note at bottom (FRS 102 cash-flow exemption).</t>
+          <t>Bank (Company-only) basis, £'000. FY2023-FY2025 state the FRS 102 cash-flow exemption in place of figures - see source note at bottom.</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6378,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>FY2023-FY2025: no Statement of Cash Flows is published - FRS 102 exemption (see note below)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -6389,205 +6390,241 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Loss on operating activities before tax</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n">
-        <v>-6933</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>-18030</v>
-      </c>
+          <t>Statement of Cash Flows</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Not published - qualifying entity under FRS 102; Section 7 / para 3.17(d) exemption taken from FY2023 onward</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Not published - qualifying entity under FRS 102; Section 7 / para 3.17(d) exemption taken from FY2023 onward</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Not published - qualifying entity under FRS 102; Section 7 / para 3.17(d) exemption taken from FY2023 onward</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Non-cash items included in loss on operating activities before tax</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n">
-        <v>11707</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>2173</v>
-      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Change in operating assets and liabilities</t>
+          <t>Loss on operating activities before tax</t>
         </is>
       </c>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n">
-        <v>304576</v>
+        <v>-6933</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>217383</v>
+        <v>-18030</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Net Cash Generated from Operating Activities</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n">
-        <v>309350</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>201526</v>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Non-cash items included in loss on operating activities before tax</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n">
+        <v>11707</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>2173</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Investing activities</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Change in operating assets and liabilities</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="E9" s="6" t="n">
+        <v>304576</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>217383</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>(Purchase)/sale of debt securities</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n">
-        <v>-61572</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>-2075</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net Cash Generated from Operating Activities</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n">
+        <v>309350</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>201526</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Net Cash Used in Investing Activities</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n">
-        <v>-61572</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>-2075</v>
-      </c>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>(Purchase)/sale of debt securities</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="E12" s="6" t="n">
+        <v>-61572</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-2075</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Proceeds from issuance of ordinary shares</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n">
-        <v>76464</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>12309</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Net Cash Used in Investing Activities</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n">
+        <v>-61572</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2075</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of ordinary shares</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n">
+        <v>76464</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>12309</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>Net Cash Generated from Financing Activities</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n">
         <v>76464</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>12309</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Net Increase in Cash and Cash Equivalents</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n">
-        <v>324242</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>211760</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at beginning of year</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n">
-        <v>376688</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>164928</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents at the end of the Year</t>
+          <t>Net Increase in Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n">
+        <v>324242</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>211760</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at beginning of year</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n">
+        <v>376688</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>164928</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Cash and Cash Equivalents at the end of the Year</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n">
         <v>700930</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>376688</v>
       </c>
     </row>
-    <row r="19" ht="260" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="260" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Tandem Bank Limited's own (Company-only, not Group) Statement of Cash Flows, £'000:
 FY2022: Tandem Bank Limited Annual Report and Accounts for the year ended 31 December 2022, p.45 (Statement of Cash Flows) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
@@ -6600,7 +6637,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7064,15 +7101,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7110,16 +7145,6 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -7130,8 +7155,6 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7148,8 +7171,6 @@
       <c r="D5" s="6" t="n">
         <v>150158</v>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -7166,8 +7187,6 @@
       <c r="D6" s="6" t="n">
         <v>150158</v>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7184,8 +7203,6 @@
       <c r="D7" s="6" t="n">
         <v>175438</v>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -7196,8 +7213,6 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7214,8 +7229,6 @@
       <c r="D9" s="6" t="n">
         <v>931650</v>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -7226,8 +7239,6 @@
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7250,8 +7261,6 @@
           <t>16.1%</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7274,8 +7283,6 @@
           <t>16.1%</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7298,8 +7305,6 @@
           <t>18.8%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7310,8 +7315,6 @@
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7334,8 +7337,6 @@
           <t>1.5%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7358,8 +7359,6 @@
           <t>0.5%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7382,8 +7381,6 @@
           <t>0.7%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7406,8 +7403,6 @@
           <t>10.6%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -7418,8 +7413,6 @@
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -7442,8 +7435,6 @@
           <t>2.5%</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -7466,8 +7457,6 @@
           <t>1.9%</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -7490,8 +7479,6 @@
           <t>4.4%</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -7514,8 +7501,6 @@
           <t>15.0%</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -7538,8 +7523,6 @@
           <t>12.9%</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -7550,8 +7533,6 @@
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -7568,8 +7549,6 @@
       <c r="D26" s="6" t="n">
         <v>1458860</v>
       </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -7592,8 +7571,6 @@
           <t>9.8%</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -7604,8 +7581,6 @@
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -7622,8 +7597,6 @@
       <c r="D29" s="6" t="n">
         <v>1786879</v>
       </c>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -7640,8 +7613,6 @@
       <c r="D30" s="6" t="n">
         <v>348061</v>
       </c>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -7658,8 +7629,6 @@
       <c r="D31" s="6" t="n">
         <v>66597</v>
       </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -7676,8 +7645,6 @@
       <c r="D32" s="6" t="n">
         <v>281464</v>
       </c>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -7700,8 +7667,6 @@
           <t>636.0%</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -7712,8 +7677,6 @@
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -7730,8 +7693,6 @@
       <c r="D35" s="6" t="n">
         <v>3142854</v>
       </c>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -7748,8 +7709,6 @@
       <c r="D36" s="6" t="n">
         <v>1156379</v>
       </c>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -7772,8 +7731,6 @@
           <t>270.6%</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
     </row>
     <row r="39" ht="300" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
@@ -7799,7 +7756,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/TANDEM FINANCIALS.xlsx
+++ b/banks/TANDEM FINANCIALS.xlsx
@@ -4202,7 +4202,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – TML Pillar 3 2021 names the NSFR only as a risk-appetite limit (&gt; 120%) and prints no ratio (text-searched 2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -4302,27 +4302,27 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – absent from BoE 'External MRELs' disclosures 2023-2026, which list every UK resolution entity with MREL above minimum capital (MCR); MREL = MCR</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – absent from BoE 'External MRELs' disclosures 2023-2026, which list every UK resolution entity with MREL above minimum capital (MCR); MREL = MCR</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – absent from BoE 'External MRELs' disclosures 2023-2026, which list every UK resolution entity with MREL above minimum capital (MCR); MREL = MCR</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no FY2022 Pillar 3 edition found (newsroom, web search, Wayback); the FY2023 edition's Dec-22 comparative has no MREL (text-searched 2026-09-19)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or mention in TML Pillar 3 2021 (text-searched 2026-09-19)</t>
         </is>
       </c>
     </row>

--- a/banks/TANDEM FINANCIALS.xlsx
+++ b/banks/TANDEM FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2926,9 +2926,13 @@
           <t>155.5%</t>
         </is>
       </c>
-      <c r="F38" s="6" t="n"/>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Not published – TML Pillar 3 2021 names the NSFR only as a risk-appetite limit (&gt; 120%) and prints no ratio (text-searched 2026-09-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="52" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Cash flow is blank for FY2023-FY2025 (FRS 102 qualifying-entity exemption took effect from FY2023 - see Cash Flow Statement sheet note) and ratios are on a wider TML Group basis, not Tandem Bank Limited solo (see each Pillar 3 sheet's source note) - two different, independently-documented basis differences within this single workbook.</t>
@@ -3029,14 +3033,14 @@
         <v>39742</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Tier 1 Capital = CET1 Capital every year through FY2022 (no AT1 instruments); AT1 capital was first issued in FY2023 but is included within Total Capital, not Tier 1, per the Group's own KM1 template (rows 1 and 2 are identical every year) - Total Capital is the row where AT1/T2 shows up as a difference.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="170" customHeight="1">
+    <row r="7" ht="195" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -3153,7 +3157,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="195" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -3259,7 +3263,7 @@
         <v>39742</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="195" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -3375,7 +3379,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="195" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -3481,7 +3485,7 @@
         <v>280843</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="195" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -3878,14 +3882,14 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="65" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021's Pillar 3 report predates the 'excluding claims on central banks' UK leverage framework (introduced Jan 2021 but not yet reflected in TML's own template that year) - its Table LRCom shows a single 'Total Leverage Ratio Exposures' / 'Leverage Ratio' figure (859,746 / 4.6%), shown here on the 'excluding' row for comparability with later years, though it is not confirmed to be on an identical basis. The FY2024 Pillar 3 report's own comparative column restates FY2023's exposure measure to 1,529,033 (footnoted 'Restated'); the figure shown here for FY2023 (1,458,860 / 9.8%) is as originally reported in the FY2023 Pillar 3 Disclosures itself, not the later restated comparative.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="170" customHeight="1">
+    <row r="8" ht="195" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -4042,14 +4046,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="65" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2022-FY2025 LCR is a simple average of monthly liquidity positions during the calendar year (per each report's own footnote). FY2021 used a different methodology (simple average of month-end observations over the trailing 12 months up to each quarter-end); the Group's FY2021 report only tabulates quarterly LCR values (31%: Dec '21 = 331%, Sep '21 = 394%, Jun '21 = 709%, Mar '21 = 1,832%) rather than one annual figure - the 31 Dec 2021 (year-end) value is shown here for comparability, but the two methodologies are not identical so a direct FY2021-to-FY2022 LCR comparison should be treated with caution. No HQLA/cash-outflow £ breakdown was found for FY2021 (only the % ratio was tabulated).</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="170" customHeight="1">
+    <row r="9" ht="195" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -4206,14 +4210,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: NSFR not disclosed for FY2021 - not yet part of TML's Pillar 3 template that year (consistent with the UK NSFR requirement not applying to reporting periods that early elsewhere in this project, e.g. Zopa).</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="170" customHeight="1">
+    <row r="9" ht="195" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -4326,14 +4330,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="104" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: MREL is not disclosed in any of TML's Pillar 3 Disclosures FY2021-FY2025. The Group states (FY2023 Pillar 3 Disclosures, Overview) that it qualifies as a 'small, non-complex' institution under UK CRR Article 4(145) and follows the reduced Pillar 3 disclosure regime of Article 433(b) - consistent with, though not an explicit stated reason for, the absence of any MREL figure. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): the missing stated reason is now supplied from outside the bank's own documents. The Bank of England's 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures (2023, 2024, 2025 and 2026 editions, at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt;) contain 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated', in the BoE's own words, and Tandem is named in none of them. So the absence of an MREL figure reflects there being no MREL above minimum capital requirement to report, not a gap in the reduced Article 433(b) disclosure set. The BoE publishes the requirement, not the ratio, so nothing from that table is transcribed here.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="195" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -4361,7 +4365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -5004,7 +5008,7 @@
         <v>853719</v>
       </c>
     </row>
-    <row r="34" ht="280" customHeight="1">
+    <row r="34" ht="351" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Tandem Bank Limited's own (Company-only, not TML Group) figures, £'000:
@@ -5014,13 +5018,21 @@
 FY2022: Annual Report and Accounts for the year ended 31 December 2022, p.43 (Statement of Financial Position), p.42 (Income Statement and Statement of Other Comprehensive Income), p.44 (Statement of Changes in Equity) - as originally reported, NOT the FY2023 Annual Report's later restated comparative - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
 FY2021: Annual Report and Accounts for the year ended 31 December 2021, p.46 (Income Statement and Statement of Other Comprehensive Income), p.47 (Statement of Financial Position), p.48 (Statement of Changes in Equity) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history
 ENTITY NOTE: 'Tandem Bank Limited' (company number 00955491, FRN 204479) is the PRA-authorised entity built here. It is NOT the same company as 'Tandem Money Limited' (company number 08628614) - a related, similarly-named entity that briefly used the name 'Tandem Bank Limited' itself from Dec 2015-May 2017 before becoming Tandem Money Limited (TML), the non-bank holding company that today sits above Tandem Bank Limited (TBL) in the group structure. Company 00955491 was previously 'Harrods Bank Limited' (renamed 12 Jan 2018) - Tandem acquired Harrods Bank's banking licence in 2017 to become a PRA-authorised deposit-taker quickly; it traces further back to 'Harrods Trust Limited' and, before that, 'Harrods (Knightsbridge) Limited' (incorporated 1969), which is why Companies House shows an incorporation date decades before Tandem's own 2013 founding. Confirmed via Companies House (previous-names history) and cross-checked against the FRN in Banks List 2608.xlsx.
-RESTATEMENT NOTE: FY2022's Balance Sheet, Profit &amp; Loss and Statement of Changes in Equity figures shown here are Tandem Bank Limited's own AS-ORIGINALLY-PUBLISHED figures (from the FY2022 Annual Report and Accounts), not the later FY2023 Annual Report's restated FY2022 comparative column (which reclassified certain effective interest rate balances and reflected motor finance hire purchase receivables as secured rather than unsecured lending - Note 2 of the FY2023 Annual Report). This creates a genuine, documented, non-plugged break at the FY2022/FY2023 boundary on the Statement of Changes in Equity sheet: FY2022's own closing Total equity (£115,178k) does not equal the FY2023 Annual Report's restated FY2023 opening balance (£115,535k, a £357k difference, itself split into a +£1,737k Other Reserves capital-contribution reclassification and a -£1,380k Retained earnings adjustment) - both figures are shown, connected by an explicit 'Restatement (per Note 2 of the FY2023 Annual Report)' row rather than silently smoothed over. The same restatement affects Loans and advances to customers on the Balance Sheet (FY2022 shown here as £1,078,369k as originally reported vs. £1,080,282k in the FY2023 Annual Report's restated comparative) and the FY2022 Profit &amp; Loss (originally reported: Interest income £74,932k, Loss on operating activities before tax £(6,933)k, Loss for the year £(1,654)k; FY2023 Annual Report's restated comparative: Interest income £72,374k, Loss before tax £(9,491)k, Loss for the year £(4,212)k).
+RESTATEMENT NOTE: FY2022's Balance Sheet, Profit &amp; Loss and Statement of Changes in Equity figures shown here are Tandem Bank Limited's own AS-ORIGINALLY-PUBLISHED figures (from the FY2022 Annual Report and Accounts), not the later FY2023 Annual Report's restated FY2022 comparative column (which reclassified certain effective interest rate balances and reflected motor finance hire purchase receivables as secured rather than unsecured lending - Note 2 of the FY2023 Annual Report). This creates a genuine, documented, non-plugged break at the FY2022/FY2023 boundary on the Statement of Changes in Equity sheet: FY2022's own closing Total equity (£115,178k) does not equal the FY2023 Annual Report's restated FY2023 opening balance (£115,535k, a £357k difference, itself split into a +£1,737k Other Reserves capital-contribution reclassification and a -£1,380k Retained earnings adjustment) - both figures are shown, connected by an explicit 'Restatement (per Note 2 of the FY2023 Annual Report)' row rather than silently smoothed over. The same restatement affects Loans and advances to customers on the Balance Sheet (FY2022 shown here as £1,078,369k as originally reported vs. £1,080,282k in the FY2023 Annual Report's restated comparative) and the FY2022 Profit &amp; Loss (originally reported: Interest income £74,932k, Loss on operating activities before tax £(6,933)k, Loss for the year £(1,654)k; FY2023 Annual Report's restated comparative: Interest income £72,374k, Loss before tax £(9,491)k, Loss for the year £(4,212)k).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="280" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 DEBT SECURITIES BREAKDOWN NOTE: the amortised-cost/available-for-sale and UK Government/other sub-rows beneath 'Total debt securities' are drawn from the Bank's own 'Debt Securities' note, not estimated: FY2025/FY2024 from Note 12 (Debt Securities), p.42 of the FY2025 Annual Report - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history; FY2023/FY2022 (as originally reported in that year's own filing) from Note 12, p.50 of the FY2023 Annual Report - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history; FY2021 from Note 15, p.61 of the FY2022 Annual Report (that filing's own '2021' comparative column) - https://find-and-update.company-information.service.gov.uk/company/00955491/filing-history. From FY2025, the note also splits out amortised-cost holdings (Mortgage Backed Loan Notes Class A and Vertical Risk Retention Notes issued by the Bank's own securitisation vehicles, Fylde Funding 2025-1 PLC and predecessors) that did not exist in FY2021-FY2023, when the entire debt securities book was held available-for-sale at market value for liquidity purposes; FY2024's 'UK Government' leg is a genuine disclosed nil (the note shows '-'), not a missing value.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A34:F34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5542,7 +5554,7 @@
         <v>-17707</v>
       </c>
     </row>
-    <row r="27" ht="300" customHeight="1">
+    <row r="27" ht="390" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Tandem Bank Limited's own (Company-only, not TML Group) figures, £'000:
@@ -6290,7 +6302,7 @@
         <v>187930</v>
       </c>
     </row>
-    <row r="43" ht="300" customHeight="1">
+    <row r="43" ht="403" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Tandem Bank Limited's own (Company-only, not TML Group) figures, £'000:
@@ -7101,7 +7113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -7732,7 +7744,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="300" customHeight="1">
+    <row r="39" ht="312" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) GROUP consolidated basis (TML + Tandem Bank Limited + Allium Lending Group Limited), NOT Tandem Bank Limited solo. The Group's own 'Key metrics table (UK KM1)', section 2 'Key Metrics', taken from EACH YEAR'S OWN edition rather than from any later edition's comparative column:
@@ -7743,11 +7755,25 @@
 RESTATEMENTS FOUND AND DELIBERATELY NOT USED - THIS IS WHY EACH COLUMN COMES FROM ITS OWN EDITION.
   * Row 12, FY2024. The FY2024 edition prints 14.68% for 31 Dec '24. The FY2025 edition's 31 Dec '24 comparative prints 11.86% and footnotes it '2024 ratio restated'. 14.68% is shown above, per this workbook's convention; the restated figure remains visible in the FY2025 document.
   * Rows 13 and 14, FY2023. The FY2023 edition prints an exposure measure of 1,458,860 and a leverage ratio of 9.8%. The FY2024 edition's 31 Dec '23 comparative prints 1,529,033 and 9.82%, both footnoted 'Restated'. The FY2023 edition's own figures are shown above.
-  * The whole FY2023 SREP/buffer block is printed to one decimal place in its own edition (UK 7a 1.5%, UK 7b 0.5%, UK 7c 0.7%, UK 7d 10.6%, row 9 1.9%, row 11 4.4%, UK 11a 15.0%, row 12 12.9%) and to two decimals in the FY2024 edition's comparative (1.45% / 0.48% / 0.65% / 10.58% / 1.94% / 4.44% / 15.02% / 12.88%). These are not rounding artefacts to be tidied: PRECISION IS THE BANK'S OWN and the FY2023 column above keeps the FY2023 edition's one-decimal house style throughout, including LCR 636.0% (534.75%-style two-decimal printing starts with the FY2024 edition) and NSFR 270.6%.
+  * The whole FY2023 SREP/buffer block is printed to one decimal place in its own edition (UK 7a 1.5%, UK 7b 0.5%, UK 7c 0.7%, UK 7d 10.6%, row 9 1.9%, row 11 4.4%, UK 11a 15.0%, row 12 12.9%) and to two decimals in the FY2024 edition's comparative (1.45% / 0.48% / 0.65% / 10.58% / 1.94% / 4.44% / 15.02% / 12.88%). These are not rounding artefacts to be tidied: PRECISION IS THE BANK'S OWN and the FY2023 column above keeps the FY2023 edition's one-decimal house style throughout, including LCR 636.0% (534.75%-style two-decimal printing starts with the FY2024 edition) and NSFR 270.6%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="338" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2022 IS BLANK, AND A FULL FY2022 KM1 COLUMN DOES EXIST - AS THE FY2023 EDITION'S COMPARATIVE - AND IS DELIBERATELY NOT USED. No standalone Pillar 3 edition for 31 December 2022 was ever published: Tandem's own newsroom (checked 2026-09-16, see above) lists 2023, 2024 and 2025 only, and the 2021 edition sits on the older assets.website-files.com CDN and is no longer linked from the newsroom at all. Every column on this sheet comes from the edition in which that year is the reporting year, and there is no such edition for FY2022. For the record, the FY2023 edition's '31 Dec '22' column prints: CET1 / Tier 1 / Total capital all 119,883; RWEA 790,158; CET1, Tier 1 and Total capital ratios all 15.2%; UK 7a-7d 1.5% / 0.5% / 0.7% / 10.6%; row 8 2.5%; row 9 1.0%; row 11 3.5%; UK 11a 14.1%; row 12 9.2%; row 13 1,401,205; row 14 8.8%; row 15 329,806; UK 16a 158,136; UK 16b 54,989; row 16 103,147; row 17 314.1%; row 18 1,447,618; row 19 922,410; row 20 155.5%. Those figures DO appear on this workbook's single-metric sheets, captioned there as coming from the FY2023 edition's comparative column - that is a different presentation from reproducing a template Tandem never published for that date, which is why they are not carried here.
 FY2021 IS BLANK BECAUSE THE TEMPLATE IS NOT USED, NOT BECAUSE NO PILLAR 3 EXISTS. TML published a full Pillar 3 report for 31 December 2021 (https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf; re-read in full 2026-09-16, 139,114 characters of clean text). It contains no KM1. Its section 4 'Capital Disclosures' (printed p.21, located from the document's OWN table of contents rather than by scanning for digits) opens with a table headed 'Key Regulatory Metrics' - but that table has exactly FOUR unnumbered rows (CET1 Capital 39,742; Total Risk Weighted Assets 280,843; CET1 Capital Ratio 14.2%; Leverage Ratio 4.6%, with a 31 December 2020 comparative). Four rows with no SREP block, no buffer block, no LCR rows and no NSFR rows is a different and much shorter table, not an unnumbered KM1, so mapping it onto template row numbers would invent a correspondence Tandem never published. Its figures appear on the single-metric sheets instead, captioned as their own edition printed them. Supporting whole-document counts, all case-insensitive, on an extraction shown to be RICH on neighbouring terms ('capital' 90, 'ratio' 120, 'cet1' 15, 'buffer' 22, 'leverage' 14) so the zeroes are facts about the document and not a failed instrument: 'km1' 0, 'srep' 0, 'UK 7a' 0, 'available own funds' 0, 'risk-weighted exposure' 0.
 ROWS TANDEM DOES NOT PRINT ARE ABSENT, NOT ZERO. All three editions omit row 10 (G-SII buffer), UK 8a, UK 9a and UK 10a, and rows 21-23, entirely - there is no cell, no dash and no zero to reproduce - so they are not shown here at all rather than shown blank.
-NO LEVERAGE BASIS BREAK TO CARRY. Tandem's first KM1 edition is FY2023, already after the 1 January 2022 UK leverage change, so rows 13/14 carry the 'excluding Claims on Central Banks' caption in all three editions and need only one caption block. (The Group states in each edition that it remains OUTSIDE the scope of the full UK Leverage Ratio Framework.) The unit is £'000 in all three editions, so no two-unit caption block is needed either.
+NO LEVERAGE BASIS BREAK TO CARRY. Tandem's first KM1 edition is FY2023, already after the 1 January 2022 UK leverage change, so rows 13/14 carry the 'excluding Claims on Central Banks' caption in all three editions and need only one caption block. (The Group states in each edition that it remains OUTSIDE the scope of the full UK Leverage Ratio Framework.) The unit is £'000 in all three editions, so no two-unit caption block is needed either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="300" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 THE TEMPLATE'S OWN FOOTNOTES, WHICH QUALIFY ROWS 15-20 IN EVERY EDITION: the LCR block is 'calculated as average of monthly liquidity positions during' the year and the NSFR block 'as average of quarterly NSFR positions during' the year - so rows 15-20 are AVERAGES, not point-in-time year-end figures, while rows 1-14 are point-in-time. Row 12 is defined by the Group as 'CET1 ratio less the minimum amount of CET1 required to meet the total SREP own funds requirement (56.25% of Pillar 1 and Pillar 2A capital requirements)', and the SREP block footnote reads 'Of which 56.25% of CET1 capital, 43.75% of AT1 capital and 25% of Tier 2 capital'.
 ENTITY NOTE: 'Tandem Bank Limited' (company number 00955491, FRN 204479) is the PRA-authorised entity built here. It is NOT the same company as 'Tandem Money Limited' (company number 08628614) - a related, similarly-named entity that briefly used the name 'Tandem Bank Limited' itself from Dec 2015-May 2017 before becoming Tandem Money Limited (TML), the non-bank holding company that today sits above Tandem Bank Limited (TBL) in the group structure. Company 00955491 was previously 'Harrods Bank Limited' (renamed 12 Jan 2018) - Tandem acquired Harrods Bank's banking licence in 2017 to become a PRA-authorised deposit-taker quickly; it traces further back to 'Harrods Trust Limited' and, before that, 'Harrods (Knightsbridge) Limited' (incorporated 1969), which is why Companies House shows an incorporation date decades before Tandem's own 2013 founding. Confirmed via Companies House (previous-names history) and cross-checked against the FRN in Banks List 2608.xlsx.
 PILLAR 3 BASIS NOTE: this sheet is TML GROUP consolidated, whereas the four statement sheets in this workbook are Tandem Bank Limited solo. Tandem does not publish a Bank-only Pillar 3 breakout, so the basis mismatch is the group's own and cannot be closed.</t>
@@ -7755,7 +7781,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7847,7 +7875,7 @@
         <v>39742</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="195" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
@@ -7963,7 +7991,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="195" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:

--- a/banks/TANDEM FINANCIALS.xlsx
+++ b/banks/TANDEM FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2954,6 +2955,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — CET1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group basis, % of RWEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.53%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.40%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="195" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3057,122 +3174,6 @@
   <mergeCells count="2">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tandem Bank Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TML Group basis, % of RWEA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.53%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.40%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="195" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3198,14 +3199,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Total Capital</t>
+          <t>Tandem Bank Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, £'000</t>
+          <t>TML Group basis, % of RWEA</t>
         </is>
       </c>
     </row>
@@ -3244,23 +3245,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>196155</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>192343</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>175438</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>119883</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>39742</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>15.53%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>17.40%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="195" customHeight="1">
@@ -3304,14 +3315,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Total Capital Ratio</t>
+          <t>Tandem Bank Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, % of RWEA</t>
+          <t>TML Group basis, £'000</t>
         </is>
       </c>
     </row>
@@ -3350,33 +3361,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>18.11%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.21%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>18.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>196155</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>192343</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>175438</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>119883</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>39742</v>
       </c>
     </row>
     <row r="6" ht="195" customHeight="1">
@@ -3420,14 +3421,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — Total RWAs</t>
+          <t>Tandem Bank Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, £'000</t>
+          <t>TML Group basis, % of RWEA</t>
         </is>
       </c>
     </row>
@@ -3466,23 +3467,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted assets (RWEA)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1083333</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>951607</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>931650</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>790158</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>280843</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>18.11%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.21%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="195" customHeight="1">
@@ -3507,6 +3518,112 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group basis, £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted assets (RWEA)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1083333</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>951607</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>931650</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>790158</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>280843</v>
+      </c>
+    </row>
+    <row r="6" ht="195" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3765,7 +3882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3906,170 +4023,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tandem Bank Limited — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TML Group basis, £'000 / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total high-quality liquid assets (HQLA), weighted value (average)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1148813</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1927554</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1786879</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>329806</v>
-      </c>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflows, adjusted value</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>258152</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>359743</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>281464</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>103147</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>443.40%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>534.75%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>636.0%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>314.1%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>331%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2022-FY2025 LCR is a simple average of monthly liquidity positions during the calendar year (per each report's own footnote). FY2021 used a different methodology (simple average of month-end observations over the trailing 12 months up to each quarter-end); the Group's FY2021 report only tabulates quarterly LCR values (31%: Dec '21 = 331%, Sep '21 = 394%, Jun '21 = 709%, Mar '21 = 1,832%) rather than one annual figure - the 31 Dec 2021 (year-end) value is shown here for comparability, but the two methodologies are not identical so a direct FY2021-to-FY2022 LCR comparison should be treated with caution. No HQLA/cash-outflow £ breakdown was found for FY2021 (only the % ratio was tabulated).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="195" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4095,7 +4048,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — NSFR</t>
+          <t>Tandem Bank Limited — LCR</t>
         </is>
       </c>
     </row>
@@ -4141,79 +4094,79 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding</t>
+          <t>Total high-quality liquid assets (HQLA), weighted value (average)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2560820</v>
+        <v>1148813</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3156347</v>
+        <v>1927554</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3142854</v>
+        <v>1786879</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1447618</v>
+        <v>329806</v>
       </c>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total required stable funding</t>
+          <t>Total net cash outflows, adjusted value</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1320668</v>
+        <v>258152</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1199958</v>
+        <v>359743</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1156379</v>
+        <v>281464</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>922410</v>
+        <v>103147</v>
       </c>
       <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>NSFR ratio (%)</t>
+          <t>Liquidity Coverage Ratio (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>194.30%</t>
+          <t>443.40%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>263.10%</t>
+          <t>534.75%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>270.6%</t>
+          <t>636.0%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>155.5%</t>
+          <t>314.1%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not published – TML Pillar 3 2021 names the NSFR only as a risk-appetite limit (&gt; 120%) and prints no ratio (text-searched 2026-09-19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>331%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: NSFR not disclosed for FY2021 - not yet part of TML's Pillar 3 template that year (consistent with the UK NSFR requirement not applying to reporting periods that early elsewhere in this project, e.g. Zopa).</t>
+          <t>Note: FY2022-FY2025 LCR is a simple average of monthly liquidity positions during the calendar year (per each report's own footnote). FY2021 used a different methodology (simple average of month-end observations over the trailing 12 months up to each quarter-end); the Group's FY2021 report only tabulates quarterly LCR values (31%: Dec '21 = 331%, Sep '21 = 394%, Jun '21 = 709%, Mar '21 = 1,832%) rather than one annual figure - the 31 Dec 2021 (year-end) value is shown here for comparability, but the two methodologies are not identical so a direct FY2021-to-FY2022 LCR comparison should be treated with caution. No HQLA/cash-outflow £ breakdown was found for FY2021 (only the % ratio was tabulated).</t>
         </is>
       </c>
     </row>
@@ -4245,10 +4198,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -4259,12 +4212,16 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — MREL Ratio</t>
+          <t>Tandem Bank Limited — NSFR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TML Group basis, £'000 / %</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -4301,44 +4258,84 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – absent from BoE 'External MRELs' disclosures 2023-2026, which list every UK resolution entity with MREL above minimum capital (MCR); MREL = MCR</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – absent from BoE 'External MRELs' disclosures 2023-2026, which list every UK resolution entity with MREL above minimum capital (MCR); MREL = MCR</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – absent from BoE 'External MRELs' disclosures 2023-2026, which list every UK resolution entity with MREL above minimum capital (MCR); MREL = MCR</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no FY2022 Pillar 3 edition found (newsroom, web search, Wayback); the FY2023 edition's Dec-22 comparative has no MREL (text-searched 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or mention in TML Pillar 3 2021 (text-searched 2026-09-19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="104" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: MREL is not disclosed in any of TML's Pillar 3 Disclosures FY2021-FY2025. The Group states (FY2023 Pillar 3 Disclosures, Overview) that it qualifies as a 'small, non-complex' institution under UK CRR Article 4(145) and follows the reduced Pillar 3 disclosure regime of Article 433(b) - consistent with, though not an explicit stated reason for, the absence of any MREL figure. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): the missing stated reason is now supplied from outside the bank's own documents. The Bank of England's 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures (2023, 2024, 2025 and 2026 editions, at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt;) contain 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated', in the BoE's own words, and Tandem is named in none of them. So the absence of an MREL figure reflects there being no MREL above minimum capital requirement to report, not a gap in the reduced Article 433(b) disclosure set. The BoE publishes the requirement, not the ratio, so nothing from that table is transcribed here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="195" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Total available stable funding</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2560820</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3156347</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3142854</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1447618</v>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1320668</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1199958</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1156379</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>922410</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>194.30%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>263.10%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>270.6%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>155.5%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not published – TML Pillar 3 2021 names the NSFR only as a risk-appetite limit (&gt; 120%) and prints no ratio (text-searched 2026-09-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: NSFR not disclosed for FY2021 - not yet part of TML's Pillar 3 template that year (consistent with the UK NSFR requirement not applying to reporting periods that early elsewhere in this project, e.g. Zopa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="195" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
 FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
@@ -4352,8 +4349,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5034,6 +5031,126 @@
   <mergeCells count="2">
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A34:F34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – absent from BoE 'External MRELs' disclosures 2023-2026, which list every UK resolution entity with MREL above minimum capital (MCR); MREL = MCR</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – absent from BoE 'External MRELs' disclosures 2023-2026, which list every UK resolution entity with MREL above minimum capital (MCR); MREL = MCR</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – absent from BoE 'External MRELs' disclosures 2023-2026, which list every UK resolution entity with MREL above minimum capital (MCR); MREL = MCR</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no FY2022 Pillar 3 edition found (newsroom, web search, Wayback); the FY2023 edition's Dec-22 comparative has no MREL (text-searched 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or mention in TML Pillar 3 2021 (text-searched 2026-09-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="104" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: MREL is not disclosed in any of TML's Pillar 3 Disclosures FY2021-FY2025. The Group states (FY2023 Pillar 3 Disclosures, Overview) that it qualifies as a 'small, non-complex' institution under UK CRR Article 4(145) and follows the reduced Pillar 3 disclosure regime of Article 433(b) - consistent with, though not an explicit stated reason for, the absence of any MREL figure. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): the missing stated reason is now supplied from outside the bank's own documents. The Bank of England's 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures (2023, 2024, 2025 and 2026 editions, at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt;) contain 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated', in the BoE's own words, and Tandem is named in none of them. So the absence of an MREL figure reflects there being no MREL above minimum capital requirement to report, not a gap in the reduced Article 433(b) disclosure set. The BoE publishes the requirement, not the ratio, so nothing from that table is transcribed here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="195" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
+FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
+FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
+FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
+FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
+PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7113,6 +7230,247 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>6.89%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>-2.11%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>6.48%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>-42.90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-2.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Tandem Bank Limited's own published return</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="182" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: COMPUTED, NOT PUBLISHED. Tandem Bank Limited publishes no explicit ROE, ROA or RoTE in its FY2025 Annual Report and Accounts. The exact 59-page image-only Companies House filing had previously been fully OCR'd with Tesseract and cross-checked against rendered page images for the Tandem workbook build; a renewed whole-report/source-trail search found no return-on-equity, return-on-assets or tangible-equity return measure. Statement values were not divided to create one. Every percentage above is therefore this project's own arithmetic on the figures printed on this workbook's statement sheets, and is labelled as such. That the bank publishes none is a POSITIVE FINDING, recorded in research/profitability/published_returns.jsonl, and not a failed search: for this bank the computed figure is the only figure there is.
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2022, where return on equity is -2.11% on an average basis and -1.44% on a year-end basis.
+FY2021 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2021 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2021 because it needs only the closing balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit/(loss) for the year” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Tandem Bank Limited's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The finding that Tandem Bank Limited publishes no return of its own is recorded in research/profitability/published_returns.jsonl under ‘TANDEM’, verified against the bank's own annual report rendered at 300 dpi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7785,112 +8143,6 @@
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A39:D39"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tandem Bank Limited — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TML Group basis, £'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>168224</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>165574</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>150158</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>119883</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>39742</v>
-      </c>
-    </row>
-    <row r="6" ht="195" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Tandem Money Limited (TML) Group consolidated basis (comprising TML, its wholly-owned subsidiary Tandem Bank Limited (TBL), and Allium Lending Group Limited) - NOT Tandem Bank Limited solo:
-FY2025: TML Pillar 3 Disclosures, 31 December 2025, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/6a1da906ea626c65de0ea1b6_TML_Pillar%203%202025%20Final.pdf
-FY2024: TML Pillar 3 Disclosures, 31 December 2024, p.4 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/680f52c61791aa8addbecd66_TML_Pillar%203%202024%20Final.pdf
-FY2023: TML Pillar 3 Disclosures, 31 December 2023, p.3 (2. Key Metrics - UK KM1) - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2022: no standalone Pillar 3 edition was found published or archived for 31 December 2022 (not on Tandem's newsroom page, not found via web search or Wayback Machine) - sourced instead from the FY2023 Pillar 3 Disclosures' own '31 Dec '22' comparative column, p.3 - https://cdn.prod.website-files.com/62b1c54534b6a11713c35c02/66a0e99ad693a6e63fe72544_TML_Pillar%203%202023%20Final.pdf
-FY2021: TML Pillar 3 Disclosures, 31 December 2021, p.21 (4. Capital Disclosures) and p.32-41 (8. Leverage / Appendix 3: Liquidity Coverage Ratio) - https://assets.website-files.com/62a364a1705cce548303c9aa/6337028c7519c4c08e1b5d54_TML_Pillar%203%202021.12.31_Board.pdf
-PILLAR 3 BASIS NOTE: this is a genuine cash-flow-vs-Pillar-3 basis mismatch (Bank-only cash flow vs. Group-level Pillar 3), the same pattern seen with Vanquis Bank Limited elsewhere in this project - Tandem does not publish a Bank-only Pillar 3 breakout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7916,14 +8168,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tandem Bank Limited — CET1 Ratio</t>
+          <t>Tandem Bank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TML Group basis, % of RWEA</t>
+          <t>TML Group basis, £'000</t>
         </is>
       </c>
     </row>
@@ -7962,33 +8214,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>15.53%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>17.40%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>168224</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>165574</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>150158</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>119883</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>39742</v>
       </c>
     </row>
     <row r="6" ht="195" customHeight="1">
